--- a/output/pdf_financials_xlsx/SSE.xlsx
+++ b/output/pdf_financials_xlsx/SSE.xlsx
@@ -1221,7 +1221,7 @@
         <v>-1.544028</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>1.052991</v>
+        <v>-1.052991</v>
       </c>
       <c r="O16" s="3" t="n">
         <v>-0.961782</v>
@@ -1237,22 +1237,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-0.203</v>
+        <v>-10.353408</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-0.332268</v>
+        <v>-3.698582</v>
       </c>
       <c r="D17" s="3" t="n">
-        <v>-0</v>
+        <v>-7.100352</v>
       </c>
       <c r="E17" s="3" t="n">
-        <v>-0.142491</v>
+        <v>-2.345885</v>
       </c>
       <c r="F17" s="3" t="n">
-        <v>-0</v>
+        <v>-0.396324</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>-4.526812</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>-0</v>
@@ -1453,22 +1453,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>5.075204</v>
+        <v>-5.075204</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>1.683157</v>
+        <v>-1.683157</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.550176</v>
+        <v>-3.550176</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>1.101697</v>
+        <v>-1.101697</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.198162</v>
+        <v>-0.198162</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.263406</v>
+        <v>-2.263406</v>
       </c>
       <c r="H20" s="1" t="inlineStr">
         <is>
@@ -1491,7 +1491,7 @@
         <v>-1.544028</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>1.052991</v>
+        <v>-1.052991</v>
       </c>
       <c r="O20" s="3" t="n">
         <v>-0.961782</v>
@@ -1611,22 +1611,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>5.075204</v>
+        <v>-5.075204</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>1.683157</v>
+        <v>-1.683157</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.550176</v>
+        <v>-3.550176</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>1.101697</v>
+        <v>-1.101697</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.198162</v>
+        <v>-0.198162</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.263406</v>
+        <v>-2.263406</v>
       </c>
       <c r="H23" s="1" t="inlineStr">
         <is>
@@ -1649,7 +1649,7 @@
         <v>-1.544028</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>1.052991</v>
+        <v>-1.052991</v>
       </c>
       <c r="O23" s="3" t="n">
         <v>-0.961782</v>
@@ -1769,13 +1769,13 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>-72.502914</v>
+        <v>72.502914</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>-84.15785</v>
+        <v>84.15785</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-118.3392</v>
+        <v>118.3392</v>
       </c>
       <c r="E26" s="1" t="inlineStr">
         <is>
@@ -1783,10 +1783,10 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>9.908099999999999</v>
+        <v>-9.908099999999999</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>16.167186</v>
+        <v>-16.167186</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>-1.544028</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>1.052991</v>
+        <v>-1.052991</v>
       </c>
       <c r="O27" s="3" t="n">
         <v>-0.961782</v>
@@ -1979,7 +1979,7 @@
         <v>-1.544028</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>1.052991</v>
+        <v>-1.052991</v>
       </c>
       <c r="O29" s="3" t="n">
         <v>-0.961782</v>
@@ -2073,22 +2073,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>3.846005194191054</v>
+        <v>196.153994805809</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>16.48624979842961</v>
+        <v>183.5137502015704</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>11.45252968200947</v>
+        <v>188.5474703179905</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H31" s="1" t="inlineStr">
         <is>
@@ -2111,7 +2111,7 @@
         <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
         <v>-0</v>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>10244.65886152604</v>
+        <v>-10244.65886152604</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1532.553015196627</v>
+        <v>-1532.553015196627</v>
       </c>
       <c r="D32" s="1" t="inlineStr">
         <is>
@@ -5415,31 +5415,31 @@
         <v>6.37225</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>6.958213</v>
+        <v>0.7399250000000001</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.596377</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.028596</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.059183</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.073905</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.359214</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.5945510000000001</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.420684</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.420684</v>
       </c>
       <c r="L92" s="1" t="inlineStr">
         <is>
@@ -5447,16 +5447,16 @@
         </is>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>1.825816</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>1.693517</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>1.148694</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.841361</v>
       </c>
     </row>
     <row r="93">
@@ -6762,7 +6762,7 @@
         <v>0</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0</v>
+        <v>1.886</v>
       </c>
       <c r="H118" s="3" t="n">
         <v>0</v>
@@ -9317,7 +9317,11 @@
           <t>Warrant reserve (Note 10) 673,093</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11879,7 +11883,11 @@
           <t>Warrant reserve (Note 11) 841,361</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -14101,7 +14109,11 @@
           <t>Warrant reserve (Note 11) 1,148,694</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" t="inlineStr">
         <is>
           <t>-</t>
@@ -16238,7 +16250,11 @@
           <t>Warrant reserve (Note 11) 1,693,517</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -18565,7 +18581,11 @@
           <t>Warrant reserve (Note 11) 444,945</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr"/>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
           <t>-</t>
@@ -20313,7 +20333,11 @@
           <t>Warrant reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -22067,7 +22091,11 @@
           <t>Warrant reserve (Note 11)</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr"/>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E158" t="inlineStr">
         <is>
           <t>-</t>
@@ -24089,7 +24117,11 @@
           <t>Warrant reserve (Note 12) 596,377</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr"/>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E180" t="inlineStr">
         <is>
           <t>-</t>
@@ -34500,7 +34532,11 @@
           <t>Non-cash exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D297" t="inlineStr"/>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
           <t>-</t>
@@ -40697,19 +40733,19 @@
         </is>
       </c>
       <c r="O366" s="5" t="n">
-        <v>2.386857</v>
+        <v>-2.386857</v>
       </c>
       <c r="P366" s="5" t="n">
-        <v>1.544028</v>
+        <v>-1.544028</v>
       </c>
       <c r="Q366" s="5" t="n">
-        <v>1.052991</v>
+        <v>-1.052991</v>
       </c>
       <c r="R366" s="5" t="n">
-        <v>0.961782</v>
+        <v>-0.961782</v>
       </c>
       <c r="S366" s="5" t="n">
-        <v>0.379909</v>
+        <v>-0.379909</v>
       </c>
     </row>
     <row r="367">
@@ -51807,10 +51843,10 @@
         </is>
       </c>
       <c r="I490" s="5" t="n">
-        <v>0.198162</v>
+        <v>-0.198162</v>
       </c>
       <c r="J490" s="5" t="n">
-        <v>2.263406</v>
+        <v>-2.263406</v>
       </c>
       <c r="K490" t="inlineStr">
         <is>
@@ -53952,16 +53988,16 @@
         </is>
       </c>
       <c r="F514" s="5" t="n">
-        <v>1.683157</v>
+        <v>-1.683157</v>
       </c>
       <c r="G514" s="5" t="n">
-        <v>3.550176</v>
+        <v>-3.550176</v>
       </c>
       <c r="H514" s="5" t="n">
-        <v>1.101697</v>
+        <v>-1.101697</v>
       </c>
       <c r="I514" s="5" t="n">
-        <v>1.013852</v>
+        <v>-1.013852</v>
       </c>
       <c r="J514" t="inlineStr">
         <is>
@@ -58939,10 +58975,10 @@
         </is>
       </c>
       <c r="E570" s="5" t="n">
-        <v>5.075204</v>
+        <v>-5.075204</v>
       </c>
       <c r="F570" s="5" t="n">
-        <v>1.384846</v>
+        <v>-1.384846</v>
       </c>
       <c r="G570" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/SSE.xlsx
+++ b/output/pdf_financials_xlsx/SSE.xlsx
@@ -872,46 +872,46 @@
         <v>5.327744</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>2.125252</v>
+        <v>2.134729</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.244935</v>
+        <v>3.62341</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.183749</v>
+        <v>1.270564</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.103453</v>
+        <v>0.202032</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.05043</v>
+        <v>2.246698</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.334994</v>
+        <v>1.307619</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.485613</v>
+        <v>0.973465</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.217671</v>
+        <v>0.691833</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.363488</v>
+        <v>0.944699</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.429384</v>
+        <v>2.310725</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.315898</v>
+        <v>1.534002</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.436216</v>
+        <v>1.001661</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.440773</v>
+        <v>0.95748</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.356255</v>
+        <v>0.414699</v>
       </c>
     </row>
     <row r="11">
@@ -924,19 +924,19 @@
         <v>-5.278204</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-2.015425</v>
+        <v>-2.024902</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.244935</v>
+        <v>-3.62341</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.183749</v>
+        <v>-1.270564</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.103453</v>
+        <v>-0.202032</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.05043</v>
+        <v>-2.246698</v>
       </c>
       <c r="H11" s="1" t="inlineStr">
         <is>
@@ -944,28 +944,28 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.485613</v>
+        <v>-0.973465</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.217671</v>
+        <v>-0.691833</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>-0.363488</v>
+        <v>-0.944699</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.429384</v>
+        <v>-2.310725</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>-0.315898</v>
+        <v>-1.534002</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.436216</v>
+        <v>-1.001661</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.440773</v>
+        <v>-0.95748</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.356255</v>
+        <v>-0.414699</v>
       </c>
     </row>
     <row r="12">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>4.2e-05</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>5.278204</v>
+        <v>5.278162</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>2.015425</v>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>5.278204</v>
+        <v>5.278162</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>2.015425</v>
@@ -1995,7 +1995,7 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>10654.42874444893</v>
+        <v>10654.34396447315</v>
       </c>
       <c r="C30" s="3" t="n">
         <v>1835.09064255602</v>
@@ -2212,34 +2212,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.216287</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.216287</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.129774</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.032723</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.116938</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.011287</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.141439</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.038956</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.008132</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.008132</v>
       </c>
       <c r="L34" s="1" t="inlineStr">
         <is>
@@ -2247,16 +2247,16 @@
         </is>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.178421</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.221929</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.377578</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.002186</v>
       </c>
     </row>
     <row r="35">
@@ -2320,34 +2320,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.216287</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.216287</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.129774</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.032723</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.116938</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.011287</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.141439</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.038956</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.008132</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.008132</v>
       </c>
       <c r="L36" s="1" t="inlineStr">
         <is>
@@ -2355,16 +2355,16 @@
         </is>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>1.178421</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.221929</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.377578</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.002186</v>
       </c>
     </row>
     <row r="37">
@@ -2968,34 +2968,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.292577</v>
+        <v>0.07629</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.292577</v>
+        <v>0.07629</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.190955</v>
+        <v>0.061181</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.068573</v>
+        <v>0.03585</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.142289</v>
+        <v>0.025351</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.013588</v>
+        <v>0.002301</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.157409</v>
+        <v>0.01597</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.141553</v>
+        <v>0.102597</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.042132</v>
+        <v>0.034</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.042132</v>
+        <v>0.034</v>
       </c>
       <c r="L48" s="1" t="inlineStr">
         <is>
@@ -3003,13 +3003,13 @@
         </is>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.230172</v>
+        <v>0.051751</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.242825</v>
+        <v>0.020896</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.379574</v>
+        <v>0.001996</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -10848,7 +10848,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -15029,7 +15029,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E127" s="5" t="n">
@@ -22732,7 +22732,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -40250,7 +40250,7 @@
       </c>
       <c r="D361" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E361" t="inlineStr">
@@ -51265,7 +51265,7 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
@@ -58059,7 +58059,7 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E560" s="5" t="n">

--- a/output/pdf_financials_xlsx/SSE.xlsx
+++ b/output/pdf_financials_xlsx/SSE.xlsx
@@ -1919,16 +1919,16 @@
         <v>0</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.017745</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.019358</v>
       </c>
       <c r="N28" s="3" t="n">
-        <v>0</v>
+        <v>0.019358</v>
       </c>
       <c r="O28" s="3" t="n">
-        <v>0</v>
+        <v>0.001612</v>
       </c>
       <c r="P28" s="3" t="n">
         <v>0</v>
@@ -1973,16 +1973,16 @@
         <v>-0.9250620000000001</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-2.386857</v>
+        <v>-2.369112</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.544028</v>
+        <v>-1.52467</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-1.052991</v>
+        <v>-1.033633</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.961782</v>
+        <v>-0.96017</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.961782</v>
@@ -5841,16 +5841,16 @@
         <v>0</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.017745</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.019358</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.019358</v>
       </c>
       <c r="O100" s="3" t="n">
-        <v>0</v>
+        <v>0.001612</v>
       </c>
       <c r="P100" s="3" t="n">
         <v>0</v>
@@ -26204,7 +26204,11 @@
           <t>Depreciation - Right-of-use asset</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E203" t="inlineStr">
         <is>
           <t>-</t>
@@ -27824,7 +27828,11 @@
           <t>Depreciation - Right-of-use asset (Note 8)</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
@@ -39746,7 +39754,11 @@
           <t>Depreciation - Right-of use asset (Note 3)</t>
         </is>
       </c>
-      <c r="D355" t="inlineStr"/>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E355" t="inlineStr">
         <is>
           <t>-</t>
@@ -42336,7 +42348,11 @@
           <t>Depreciation - Right-of use asset (Note 8)</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr"/>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E385" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SSE.xlsx
+++ b/output/pdf_financials_xlsx/SSE.xlsx
@@ -1237,10 +1237,10 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>-10.353408</v>
+        <v>0.203</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>-3.698582</v>
+        <v>0.630579</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>-7.100352</v>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>196.153994805809</v>
+        <v>3.846005194191054</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>183.5137502015704</v>
+        <v>31.28764404530062</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>200</v>
@@ -6126,7 +6126,7 @@
         <v>-0.292227</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>-0.9124139999999999</v>
+        <v>-0.103874</v>
       </c>
       <c r="D106" s="3" t="n">
         <v>0.162419</v>
@@ -6144,10 +6144,10 @@
         <v>-0.031235</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.032195</v>
+        <v>-0.002587</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.159178</v>
+        <v>0.1598</v>
       </c>
       <c r="K106" s="3" t="n">
         <v>0.040741</v>
@@ -6349,13 +6349,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="3" t="n">
-        <v>0</v>
+        <v>0.067424</v>
       </c>
       <c r="I110" s="3" t="n">
-        <v>0</v>
+        <v>0.042533</v>
       </c>
       <c r="J110" s="3" t="n">
-        <v>0</v>
+        <v>0.08630400000000001</v>
       </c>
       <c r="K110" s="3" t="n">
         <v>0</v>
@@ -6386,7 +6386,7 @@
         <v>0</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.015922</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -7612,7 +7612,7 @@
         <v>0</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -7664,7 +7664,7 @@
         <v>-0.292227</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-0.9124139999999999</v>
+        <v>-0.962414</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.44804</v>
@@ -30925,7 +30925,11 @@
           <t>Accretion</t>
         </is>
       </c>
-      <c r="D256" t="inlineStr"/>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E256" t="inlineStr">
         <is>
           <t>-</t>
@@ -31538,7 +31542,11 @@
           <t>Change in non-cash operating working capital</t>
         </is>
       </c>
-      <c r="D263" t="inlineStr"/>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>ChangeInWorkingCapital</t>
+        </is>
+      </c>
       <c r="E263" s="5" t="n">
         <v>0.332199</v>
       </c>
@@ -35266,7 +35274,11 @@
           <t>Deferred tax recovery</t>
         </is>
       </c>
-      <c r="D305" t="inlineStr"/>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E305" t="inlineStr">
         <is>
           <t>-</t>
@@ -35895,7 +35907,11 @@
           <t>Proceeds from sale of investments</t>
         </is>
       </c>
-      <c r="D312" t="inlineStr"/>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E312" t="inlineStr">
         <is>
           <t>-</t>
@@ -37610,7 +37626,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D331" t="inlineStr"/>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E331" t="inlineStr">
         <is>
           <t>-</t>
@@ -37978,7 +37998,11 @@
           <t>Recovery of future income taxes</t>
         </is>
       </c>
-      <c r="D335" t="inlineStr"/>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E335" s="5" t="n">
         <v>-0.203</v>
       </c>
@@ -58896,7 +58920,11 @@
           <t>Future income tax recovery (Note 9)</t>
         </is>
       </c>
-      <c r="D569" t="inlineStr"/>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E569" s="5" t="n">
         <v>-0.203</v>
       </c>
